--- a/csvpp_app/filelist2xls.xlsx
+++ b/csvpp_app/filelist2xls.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="cmd" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="177">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -243,15 +243,30 @@
     <t xml:space="preserve">%fclose</t>
   </si>
   <si>
+    <t xml:space="preserve">w_office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$\office$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open</t>
+  </si>
+  <si>
     <t xml:space="preserve">%exec</t>
   </si>
   <si>
+    <t xml:space="preserve">csvmake2_ooo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"$\own_xls$"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%else</t>
+  </si>
+  <si>
     <t xml:space="preserve">csvmake2</t>
   </si>
   <si>
-    <t xml:space="preserve">"$\own_xls$"</t>
-  </si>
-  <si>
     <t xml:space="preserve">ファイルリストリカーシブ</t>
   </si>
   <si>
@@ -472,9 +487,6 @@
   </si>
   <si>
     <t xml:space="preserve">$keisen$┃,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%else</t>
   </si>
   <si>
     <t xml:space="preserve">$#g_msgno$,$keisen$┗,$file$</t>
@@ -1007,9 +1019,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>409680</xdr:colOff>
+      <xdr:colOff>409320</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>28080</xdr:rowOff>
+      <xdr:rowOff>27720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1019,7 +1031,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="837000" y="1096560"/>
-          <a:ext cx="3418200" cy="817560"/>
+          <a:ext cx="3417840" cy="817200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2112,7 +2124,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IW118"/>
+  <dimension ref="A1:IW123"/>
   <sheetFormatPr defaultColWidth="8.984375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="3.48"/>
@@ -2128,7 +2140,6 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="3.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="16.27"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="13" style="2" width="8.98"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="258" style="1" width="8.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5037,341 +5048,368 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="2" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="1"/>
+      <c r="C37" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="34"/>
-      <c r="B37" s="40" t="s">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1"/>
+      <c r="C40" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="34"/>
+      <c r="B42" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-      <c r="X37" s="34"/>
-      <c r="Y37" s="34"/>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="34"/>
-      <c r="AC37" s="34"/>
-      <c r="AD37" s="34"/>
-      <c r="AE37" s="34"/>
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="34"/>
-      <c r="AH37" s="34"/>
-      <c r="AI37" s="34"/>
-      <c r="AJ37" s="34"/>
-      <c r="AK37" s="34"/>
-      <c r="AL37" s="34"/>
-      <c r="AM37" s="34"/>
-      <c r="AN37" s="34"/>
-      <c r="AO37" s="34"/>
-      <c r="AP37" s="34"/>
-      <c r="AQ37" s="34"/>
-      <c r="AR37" s="34"/>
-      <c r="AS37" s="34"/>
-      <c r="AT37" s="34"/>
-      <c r="AU37" s="34"/>
-      <c r="AV37" s="34"/>
-      <c r="AW37" s="34"/>
-      <c r="AX37" s="34"/>
-      <c r="AY37" s="34"/>
-      <c r="AZ37" s="34"/>
-      <c r="BA37" s="34"/>
-      <c r="BB37" s="34"/>
-      <c r="BC37" s="34"/>
-      <c r="BD37" s="34"/>
-      <c r="BE37" s="34"/>
-      <c r="BF37" s="34"/>
-      <c r="BG37" s="34"/>
-      <c r="BH37" s="34"/>
-      <c r="BI37" s="34"/>
-      <c r="BJ37" s="34"/>
-      <c r="BK37" s="34"/>
-      <c r="BL37" s="34"/>
-      <c r="BM37" s="34"/>
-      <c r="BN37" s="34"/>
-      <c r="BO37" s="34"/>
-      <c r="BP37" s="34"/>
-      <c r="BQ37" s="34"/>
-      <c r="BR37" s="34"/>
-      <c r="BS37" s="34"/>
-      <c r="BT37" s="34"/>
-      <c r="BU37" s="34"/>
-      <c r="BV37" s="34"/>
-      <c r="BW37" s="34"/>
-      <c r="BX37" s="34"/>
-      <c r="BY37" s="34"/>
-      <c r="BZ37" s="34"/>
-      <c r="CA37" s="34"/>
-      <c r="CB37" s="34"/>
-      <c r="CC37" s="34"/>
-      <c r="CD37" s="34"/>
-      <c r="CE37" s="34"/>
-      <c r="CF37" s="34"/>
-      <c r="CG37" s="34"/>
-      <c r="CH37" s="34"/>
-      <c r="CI37" s="34"/>
-      <c r="CJ37" s="34"/>
-      <c r="CK37" s="34"/>
-      <c r="CL37" s="34"/>
-      <c r="CM37" s="34"/>
-      <c r="CN37" s="34"/>
-      <c r="CO37" s="34"/>
-      <c r="CP37" s="34"/>
-      <c r="CQ37" s="34"/>
-      <c r="CR37" s="34"/>
-      <c r="CS37" s="34"/>
-      <c r="CT37" s="34"/>
-      <c r="CU37" s="34"/>
-      <c r="CV37" s="34"/>
-      <c r="CW37" s="34"/>
-      <c r="CX37" s="34"/>
-      <c r="CY37" s="34"/>
-      <c r="CZ37" s="34"/>
-      <c r="DA37" s="34"/>
-      <c r="DB37" s="34"/>
-      <c r="DC37" s="34"/>
-      <c r="DD37" s="34"/>
-      <c r="DE37" s="34"/>
-      <c r="DF37" s="34"/>
-      <c r="DG37" s="34"/>
-      <c r="DH37" s="34"/>
-      <c r="DI37" s="34"/>
-      <c r="DJ37" s="34"/>
-      <c r="DK37" s="34"/>
-      <c r="DL37" s="34"/>
-      <c r="DM37" s="34"/>
-      <c r="DN37" s="34"/>
-      <c r="DO37" s="34"/>
-      <c r="DP37" s="34"/>
-      <c r="DQ37" s="34"/>
-      <c r="DR37" s="34"/>
-      <c r="DS37" s="34"/>
-      <c r="DT37" s="34"/>
-      <c r="DU37" s="34"/>
-      <c r="DV37" s="34"/>
-      <c r="DW37" s="34"/>
-      <c r="DX37" s="34"/>
-      <c r="DY37" s="34"/>
-      <c r="DZ37" s="34"/>
-      <c r="EA37" s="34"/>
-      <c r="EB37" s="34"/>
-      <c r="EC37" s="34"/>
-      <c r="ED37" s="34"/>
-      <c r="EE37" s="34"/>
-      <c r="EF37" s="34"/>
-      <c r="EG37" s="34"/>
-      <c r="EH37" s="34"/>
-      <c r="EI37" s="34"/>
-      <c r="EJ37" s="34"/>
-      <c r="EK37" s="34"/>
-      <c r="EL37" s="34"/>
-      <c r="EM37" s="34"/>
-      <c r="EN37" s="34"/>
-      <c r="EO37" s="34"/>
-      <c r="EP37" s="34"/>
-      <c r="EQ37" s="34"/>
-      <c r="ER37" s="34"/>
-      <c r="ES37" s="34"/>
-      <c r="ET37" s="34"/>
-      <c r="EU37" s="34"/>
-      <c r="EV37" s="34"/>
-      <c r="EW37" s="34"/>
-      <c r="EX37" s="34"/>
-      <c r="EY37" s="34"/>
-      <c r="EZ37" s="34"/>
-      <c r="FA37" s="34"/>
-      <c r="FB37" s="34"/>
-      <c r="FC37" s="34"/>
-      <c r="FD37" s="34"/>
-      <c r="FE37" s="34"/>
-      <c r="FF37" s="34"/>
-      <c r="FG37" s="34"/>
-      <c r="FH37" s="34"/>
-      <c r="FI37" s="34"/>
-      <c r="FJ37" s="34"/>
-      <c r="FK37" s="34"/>
-      <c r="FL37" s="34"/>
-      <c r="FM37" s="34"/>
-      <c r="FN37" s="34"/>
-      <c r="FO37" s="34"/>
-      <c r="FP37" s="34"/>
-      <c r="FQ37" s="34"/>
-      <c r="FR37" s="34"/>
-      <c r="FS37" s="34"/>
-      <c r="FT37" s="34"/>
-      <c r="FU37" s="34"/>
-      <c r="FV37" s="34"/>
-      <c r="FW37" s="34"/>
-      <c r="FX37" s="34"/>
-      <c r="FY37" s="34"/>
-      <c r="FZ37" s="34"/>
-      <c r="GA37" s="34"/>
-      <c r="GB37" s="34"/>
-      <c r="GC37" s="34"/>
-      <c r="GD37" s="34"/>
-      <c r="GE37" s="34"/>
-      <c r="GF37" s="34"/>
-      <c r="GG37" s="34"/>
-      <c r="GH37" s="34"/>
-      <c r="GI37" s="34"/>
-      <c r="GJ37" s="34"/>
-      <c r="GK37" s="34"/>
-      <c r="GL37" s="34"/>
-      <c r="GM37" s="34"/>
-      <c r="GN37" s="34"/>
-      <c r="GO37" s="34"/>
-      <c r="GP37" s="34"/>
-      <c r="GQ37" s="34"/>
-      <c r="GR37" s="34"/>
-      <c r="GS37" s="34"/>
-      <c r="GT37" s="34"/>
-      <c r="GU37" s="34"/>
-      <c r="GV37" s="34"/>
-      <c r="GW37" s="34"/>
-      <c r="GX37" s="34"/>
-      <c r="GY37" s="34"/>
-      <c r="GZ37" s="34"/>
-      <c r="HA37" s="34"/>
-      <c r="HB37" s="34"/>
-      <c r="HC37" s="34"/>
-      <c r="HD37" s="34"/>
-      <c r="HE37" s="34"/>
-      <c r="HF37" s="34"/>
-      <c r="HG37" s="34"/>
-      <c r="HH37" s="34"/>
-      <c r="HI37" s="34"/>
-      <c r="HJ37" s="34"/>
-      <c r="HK37" s="34"/>
-      <c r="HL37" s="34"/>
-      <c r="HM37" s="34"/>
-      <c r="HN37" s="34"/>
-      <c r="HO37" s="34"/>
-      <c r="HP37" s="34"/>
-      <c r="HQ37" s="34"/>
-      <c r="HR37" s="34"/>
-      <c r="HS37" s="34"/>
-      <c r="HT37" s="34"/>
-      <c r="HU37" s="34"/>
-      <c r="HV37" s="34"/>
-      <c r="HW37" s="34"/>
-      <c r="HX37" s="34"/>
-      <c r="HY37" s="34"/>
-      <c r="HZ37" s="34"/>
-      <c r="IA37" s="34"/>
-      <c r="IB37" s="34"/>
-      <c r="IC37" s="34"/>
-      <c r="ID37" s="34"/>
-      <c r="IE37" s="34"/>
-      <c r="IF37" s="34"/>
-      <c r="IG37" s="34"/>
-      <c r="IH37" s="34"/>
-      <c r="II37" s="34"/>
-      <c r="IJ37" s="34"/>
-      <c r="IK37" s="34"/>
-      <c r="IL37" s="34"/>
-      <c r="IM37" s="34"/>
-      <c r="IN37" s="34"/>
-      <c r="IO37" s="34"/>
-      <c r="IP37" s="34"/>
-      <c r="IQ37" s="34"/>
-      <c r="IR37" s="34"/>
-      <c r="IS37" s="34"/>
-      <c r="IT37" s="34"/>
-      <c r="IU37" s="34"/>
-      <c r="IV37" s="34"/>
-      <c r="IW37" s="34"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="C42" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="34"/>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="34"/>
+      <c r="X42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="34"/>
+      <c r="AA42" s="34"/>
+      <c r="AB42" s="34"/>
+      <c r="AC42" s="34"/>
+      <c r="AD42" s="34"/>
+      <c r="AE42" s="34"/>
+      <c r="AF42" s="34"/>
+      <c r="AG42" s="34"/>
+      <c r="AH42" s="34"/>
+      <c r="AI42" s="34"/>
+      <c r="AJ42" s="34"/>
+      <c r="AK42" s="34"/>
+      <c r="AL42" s="34"/>
+      <c r="AM42" s="34"/>
+      <c r="AN42" s="34"/>
+      <c r="AO42" s="34"/>
+      <c r="AP42" s="34"/>
+      <c r="AQ42" s="34"/>
+      <c r="AR42" s="34"/>
+      <c r="AS42" s="34"/>
+      <c r="AT42" s="34"/>
+      <c r="AU42" s="34"/>
+      <c r="AV42" s="34"/>
+      <c r="AW42" s="34"/>
+      <c r="AX42" s="34"/>
+      <c r="AY42" s="34"/>
+      <c r="AZ42" s="34"/>
+      <c r="BA42" s="34"/>
+      <c r="BB42" s="34"/>
+      <c r="BC42" s="34"/>
+      <c r="BD42" s="34"/>
+      <c r="BE42" s="34"/>
+      <c r="BF42" s="34"/>
+      <c r="BG42" s="34"/>
+      <c r="BH42" s="34"/>
+      <c r="BI42" s="34"/>
+      <c r="BJ42" s="34"/>
+      <c r="BK42" s="34"/>
+      <c r="BL42" s="34"/>
+      <c r="BM42" s="34"/>
+      <c r="BN42" s="34"/>
+      <c r="BO42" s="34"/>
+      <c r="BP42" s="34"/>
+      <c r="BQ42" s="34"/>
+      <c r="BR42" s="34"/>
+      <c r="BS42" s="34"/>
+      <c r="BT42" s="34"/>
+      <c r="BU42" s="34"/>
+      <c r="BV42" s="34"/>
+      <c r="BW42" s="34"/>
+      <c r="BX42" s="34"/>
+      <c r="BY42" s="34"/>
+      <c r="BZ42" s="34"/>
+      <c r="CA42" s="34"/>
+      <c r="CB42" s="34"/>
+      <c r="CC42" s="34"/>
+      <c r="CD42" s="34"/>
+      <c r="CE42" s="34"/>
+      <c r="CF42" s="34"/>
+      <c r="CG42" s="34"/>
+      <c r="CH42" s="34"/>
+      <c r="CI42" s="34"/>
+      <c r="CJ42" s="34"/>
+      <c r="CK42" s="34"/>
+      <c r="CL42" s="34"/>
+      <c r="CM42" s="34"/>
+      <c r="CN42" s="34"/>
+      <c r="CO42" s="34"/>
+      <c r="CP42" s="34"/>
+      <c r="CQ42" s="34"/>
+      <c r="CR42" s="34"/>
+      <c r="CS42" s="34"/>
+      <c r="CT42" s="34"/>
+      <c r="CU42" s="34"/>
+      <c r="CV42" s="34"/>
+      <c r="CW42" s="34"/>
+      <c r="CX42" s="34"/>
+      <c r="CY42" s="34"/>
+      <c r="CZ42" s="34"/>
+      <c r="DA42" s="34"/>
+      <c r="DB42" s="34"/>
+      <c r="DC42" s="34"/>
+      <c r="DD42" s="34"/>
+      <c r="DE42" s="34"/>
+      <c r="DF42" s="34"/>
+      <c r="DG42" s="34"/>
+      <c r="DH42" s="34"/>
+      <c r="DI42" s="34"/>
+      <c r="DJ42" s="34"/>
+      <c r="DK42" s="34"/>
+      <c r="DL42" s="34"/>
+      <c r="DM42" s="34"/>
+      <c r="DN42" s="34"/>
+      <c r="DO42" s="34"/>
+      <c r="DP42" s="34"/>
+      <c r="DQ42" s="34"/>
+      <c r="DR42" s="34"/>
+      <c r="DS42" s="34"/>
+      <c r="DT42" s="34"/>
+      <c r="DU42" s="34"/>
+      <c r="DV42" s="34"/>
+      <c r="DW42" s="34"/>
+      <c r="DX42" s="34"/>
+      <c r="DY42" s="34"/>
+      <c r="DZ42" s="34"/>
+      <c r="EA42" s="34"/>
+      <c r="EB42" s="34"/>
+      <c r="EC42" s="34"/>
+      <c r="ED42" s="34"/>
+      <c r="EE42" s="34"/>
+      <c r="EF42" s="34"/>
+      <c r="EG42" s="34"/>
+      <c r="EH42" s="34"/>
+      <c r="EI42" s="34"/>
+      <c r="EJ42" s="34"/>
+      <c r="EK42" s="34"/>
+      <c r="EL42" s="34"/>
+      <c r="EM42" s="34"/>
+      <c r="EN42" s="34"/>
+      <c r="EO42" s="34"/>
+      <c r="EP42" s="34"/>
+      <c r="EQ42" s="34"/>
+      <c r="ER42" s="34"/>
+      <c r="ES42" s="34"/>
+      <c r="ET42" s="34"/>
+      <c r="EU42" s="34"/>
+      <c r="EV42" s="34"/>
+      <c r="EW42" s="34"/>
+      <c r="EX42" s="34"/>
+      <c r="EY42" s="34"/>
+      <c r="EZ42" s="34"/>
+      <c r="FA42" s="34"/>
+      <c r="FB42" s="34"/>
+      <c r="FC42" s="34"/>
+      <c r="FD42" s="34"/>
+      <c r="FE42" s="34"/>
+      <c r="FF42" s="34"/>
+      <c r="FG42" s="34"/>
+      <c r="FH42" s="34"/>
+      <c r="FI42" s="34"/>
+      <c r="FJ42" s="34"/>
+      <c r="FK42" s="34"/>
+      <c r="FL42" s="34"/>
+      <c r="FM42" s="34"/>
+      <c r="FN42" s="34"/>
+      <c r="FO42" s="34"/>
+      <c r="FP42" s="34"/>
+      <c r="FQ42" s="34"/>
+      <c r="FR42" s="34"/>
+      <c r="FS42" s="34"/>
+      <c r="FT42" s="34"/>
+      <c r="FU42" s="34"/>
+      <c r="FV42" s="34"/>
+      <c r="FW42" s="34"/>
+      <c r="FX42" s="34"/>
+      <c r="FY42" s="34"/>
+      <c r="FZ42" s="34"/>
+      <c r="GA42" s="34"/>
+      <c r="GB42" s="34"/>
+      <c r="GC42" s="34"/>
+      <c r="GD42" s="34"/>
+      <c r="GE42" s="34"/>
+      <c r="GF42" s="34"/>
+      <c r="GG42" s="34"/>
+      <c r="GH42" s="34"/>
+      <c r="GI42" s="34"/>
+      <c r="GJ42" s="34"/>
+      <c r="GK42" s="34"/>
+      <c r="GL42" s="34"/>
+      <c r="GM42" s="34"/>
+      <c r="GN42" s="34"/>
+      <c r="GO42" s="34"/>
+      <c r="GP42" s="34"/>
+      <c r="GQ42" s="34"/>
+      <c r="GR42" s="34"/>
+      <c r="GS42" s="34"/>
+      <c r="GT42" s="34"/>
+      <c r="GU42" s="34"/>
+      <c r="GV42" s="34"/>
+      <c r="GW42" s="34"/>
+      <c r="GX42" s="34"/>
+      <c r="GY42" s="34"/>
+      <c r="GZ42" s="34"/>
+      <c r="HA42" s="34"/>
+      <c r="HB42" s="34"/>
+      <c r="HC42" s="34"/>
+      <c r="HD42" s="34"/>
+      <c r="HE42" s="34"/>
+      <c r="HF42" s="34"/>
+      <c r="HG42" s="34"/>
+      <c r="HH42" s="34"/>
+      <c r="HI42" s="34"/>
+      <c r="HJ42" s="34"/>
+      <c r="HK42" s="34"/>
+      <c r="HL42" s="34"/>
+      <c r="HM42" s="34"/>
+      <c r="HN42" s="34"/>
+      <c r="HO42" s="34"/>
+      <c r="HP42" s="34"/>
+      <c r="HQ42" s="34"/>
+      <c r="HR42" s="34"/>
+      <c r="HS42" s="34"/>
+      <c r="HT42" s="34"/>
+      <c r="HU42" s="34"/>
+      <c r="HV42" s="34"/>
+      <c r="HW42" s="34"/>
+      <c r="HX42" s="34"/>
+      <c r="HY42" s="34"/>
+      <c r="HZ42" s="34"/>
+      <c r="IA42" s="34"/>
+      <c r="IB42" s="34"/>
+      <c r="IC42" s="34"/>
+      <c r="ID42" s="34"/>
+      <c r="IE42" s="34"/>
+      <c r="IF42" s="34"/>
+      <c r="IG42" s="34"/>
+      <c r="IH42" s="34"/>
+      <c r="II42" s="34"/>
+      <c r="IJ42" s="34"/>
+      <c r="IK42" s="34"/>
+      <c r="IL42" s="34"/>
+      <c r="IM42" s="34"/>
+      <c r="IN42" s="34"/>
+      <c r="IO42" s="34"/>
+      <c r="IP42" s="34"/>
+      <c r="IQ42" s="34"/>
+      <c r="IR42" s="34"/>
+      <c r="IS42" s="34"/>
+      <c r="IT42" s="34"/>
+      <c r="IU42" s="34"/>
+      <c r="IV42" s="34"/>
+      <c r="IW42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5395,7 +5433,7 @@
         <v>28</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5403,7 +5441,7 @@
         <v>28</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5411,7 +5449,7 @@
         <v>28</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5419,1064 +5457,1104 @@
         <v>28</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>86</v>
+        <v>28</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C53" s="8" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="8" t="s">
-        <v>93</v>
+        <v>40</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="41" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C57" s="8" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="42" t="s">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F61" s="41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C58" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="13"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="8" t="s">
+      <c r="C63" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D63" s="11"/>
+      <c r="E63" s="13"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D59" s="2" t="n">
+      <c r="C64" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D60" s="2" t="n">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="E65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C66" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C67" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L67" s="44" t="s">
-        <v>117</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C68" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L68" s="44" t="s">
-        <v>119</v>
+      <c r="L68" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C69" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" s="44" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L69" s="44" t="s">
-        <v>121</v>
+        <v>115</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C70" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="44" t="s">
-        <v>122</v>
+        <v>83</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L70" s="44" t="s">
-        <v>123</v>
+      <c r="L70" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C71" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" s="44" t="s">
-        <v>124</v>
+        <v>83</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L71" s="44" t="s">
-        <v>125</v>
+      <c r="L71" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C72" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72" s="44" t="s">
-        <v>126</v>
+        <v>83</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L72" s="44" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C73" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L73" s="2" t="s">
+      <c r="L73" s="44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C74" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D74" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="44" t="s">
+        <v>125</v>
+      </c>
       <c r="F74" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" s="44" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C75" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>129</v>
+        <v>83</v>
+      </c>
+      <c r="E75" s="44" t="s">
+        <v>127</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L75" s="2" t="s">
-        <v>25</v>
+      <c r="L75" s="44" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C76" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>130</v>
+        <v>83</v>
+      </c>
+      <c r="E76" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>131</v>
+      <c r="L76" s="44" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C77" s="2" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
+      </c>
+      <c r="E77" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L77" s="44" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="D78" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>132</v>
+      <c r="G78" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="2" t="s">
-        <v>48</v>
+      <c r="F79" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C80" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C81" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D83" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C85" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="42" t="s">
+    </row>
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C86" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C84" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="D84" s="11"/>
-      <c r="E84" s="13"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="8" t="s">
+      <c r="C89" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D89" s="11"/>
+      <c r="E89" s="13"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D85" s="2" t="n">
+      <c r="C90" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" s="2" t="n">
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D91" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C88" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="E91" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C89" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C90" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C91" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E91" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C92" s="2" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="K92" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C93" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C94" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95" s="43" t="s">
-        <v>138</v>
-      </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="13"/>
+      <c r="C95" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C96" s="2" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>139</v>
+        <v>111</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>1</v>
+      <c r="C97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C99" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E100" s="11"/>
+      <c r="F100" s="13"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C101" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E98" s="2" t="n">
+      <c r="E101" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C103" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E103" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D99" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D100" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D101" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D102" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F102" s="2" t="s">
+      <c r="F103" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D103" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="s">
-        <v>107</v>
+      <c r="H103" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="2" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F104" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F105" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D106" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C106" s="2" t="s">
-        <v>93</v>
+      <c r="G106" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D107" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C108" s="42" t="s">
+      <c r="D108" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L108" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D108" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="13"/>
+      <c r="M108" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="H109" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D110" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C113" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E113" s="11"/>
+      <c r="F113" s="13"/>
+    </row>
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C114" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D116" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D117" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C118" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C110" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D111" s="2" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D119" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D112" s="2" t="s">
+      <c r="F119" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D120" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E112" s="8" t="s">
+      <c r="E120" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D114" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D115" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H115" s="2" t="s">
+      <c r="F120" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C116" s="2" t="s">
+      <c r="G120" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C117" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="2" t="s">
-        <v>93</v>
+    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C122" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -6495,7 +6573,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="46" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
@@ -6569,7 +6647,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="50" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
@@ -6608,7 +6686,7 @@
     <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="49"/>
       <c r="C5" s="49" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
@@ -6646,7 +6724,7 @@
     <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="49"/>
       <c r="C6" s="49" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
@@ -6684,7 +6762,7 @@
     <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="49"/>
       <c r="C7" s="49" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
@@ -6722,7 +6800,7 @@
     <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="49"/>
       <c r="C8" s="49" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="49"/>
@@ -6760,7 +6838,7 @@
     <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="49"/>
       <c r="C9" s="49" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="49"/>
@@ -6798,7 +6876,7 @@
     <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="49"/>
       <c r="C10" s="49" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -6872,7 +6950,7 @@
     <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="49"/>
       <c r="C12" s="49" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="49"/>
@@ -6911,7 +6989,7 @@
       <c r="B13" s="49"/>
       <c r="C13" s="49"/>
       <c r="D13" s="49" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="49"/>
@@ -6984,7 +7062,7 @@
     <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="49"/>
       <c r="C15" s="49" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D15" s="49"/>
       <c r="E15" s="49"/>
@@ -7023,7 +7101,7 @@
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
       <c r="D16" s="53" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
@@ -7094,7 +7172,7 @@
     </row>
     <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="50" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
@@ -7133,7 +7211,7 @@
     <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="49"/>
       <c r="C19" s="49" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D19" s="49"/>
       <c r="E19" s="49"/>
@@ -7171,7 +7249,7 @@
     <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="49"/>
       <c r="C20" s="49" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D20" s="49"/>
       <c r="E20" s="49"/>
@@ -7209,7 +7287,7 @@
     <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="49"/>
       <c r="C21" s="49" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D21" s="49"/>
       <c r="E21" s="49"/>
@@ -7283,7 +7361,7 @@
     <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49"/>
       <c r="B23" s="50" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -7323,7 +7401,7 @@
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
       <c r="C24" s="53" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D24" s="49"/>
       <c r="E24" s="49"/>
@@ -7362,7 +7440,7 @@
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
       <c r="C25" s="49" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D25" s="49"/>
       <c r="E25" s="49"/>
@@ -7400,7 +7478,7 @@
     <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="49"/>
       <c r="C26" s="49" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="49"/>
@@ -7437,7 +7515,7 @@
     </row>
     <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="45" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/csvpp_app/filelist2xls.xlsx
+++ b/csvpp_app/filelist2xls.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="cmd" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="173">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -243,250 +243,238 @@
     <t xml:space="preserve">%fclose</t>
   </si>
   <si>
-    <t xml:space="preserve">w_office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$\office$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">open</t>
-  </si>
-  <si>
     <t xml:space="preserve">%exec</t>
   </si>
   <si>
-    <t xml:space="preserve">csvmake2_ooo</t>
+    <t xml:space="preserve">csvmake2</t>
   </si>
   <si>
     <t xml:space="preserve">"$\own_xls$"</t>
   </si>
   <si>
+    <t xml:space="preserve">ファイルリストリカーシブ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kanma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sv_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">msg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">msgno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">last_dir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$g_msgno$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_msgno+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$cnt$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$kanma$,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%endfor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%file_get</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%printf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directory=$dir$($cnt$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File List Make</t>
+  </si>
+  <si>
+    <t xml:space="preserve">j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">j-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%aryrd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファイル名の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attr$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属性の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">file[4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$msgno$,"$file$"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">size$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$msg$,$file$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サイズの取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新日付の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新時間の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acc_date$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最終アクセス日付の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acc_time$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最終アクセス時間の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create_date$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成日付の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create_time$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作成時間の取出し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$msg$,$dir$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">link$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">link_attr$i$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">リンク先属性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$msg$\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$msg$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directory Tree Make</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">..</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$file$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Directory Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$#i+1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name$k$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attr$k$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$sv_file$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$#g_msgno$,$keisen$┣,$file$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$dir$$file$\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$#cnt+1$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$keisen$┃,</t>
+  </si>
+  <si>
     <t xml:space="preserve">%else</t>
-  </si>
-  <si>
-    <t xml:space="preserve">csvmake2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファイルリストリカーシブ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keisen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kanma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sv_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">msgno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">last_dir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$g_msgno$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%calc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g_msgno+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%for</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$cnt$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$kanma$,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%endfor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%file_get</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%printf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory=$dir$($cnt$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File List Make</t>
-  </si>
-  <si>
-    <t xml:space="preserve">j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">j-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%aryrd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファイル名の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%break</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attr$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">属性の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">file[4]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%continue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$msgno$,"$file$"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">size$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$msg$,$file$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サイズの取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">更新日付の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">更新時間の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acc_date$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最終アクセス日付の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acc_time$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最終アクセス時間の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_date$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作成日付の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">create_time$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作成時間の取出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$msg$,$dir$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">link$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">link_attr$i$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">リンク先属性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$msg$\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$msg$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory Tree Make</t>
-  </si>
-  <si>
-    <t xml:space="preserve">.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">..</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$file$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Directory Check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$#i+1$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name$k$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attr$k$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$sv_file$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$#g_msgno$,$keisen$┣,$file$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$dir$$file$\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$#cnt+1$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$keisen$┃,</t>
   </si>
   <si>
     <t xml:space="preserve">$#g_msgno$,$keisen$┗,$file$</t>
@@ -1019,9 +1007,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>409320</xdr:colOff>
+      <xdr:colOff>409680</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>27720</xdr:rowOff>
+      <xdr:rowOff>28080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1031,7 +1019,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="837000" y="1096560"/>
-          <a:ext cx="3417840" cy="817200"/>
+          <a:ext cx="3418200" cy="817560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2124,7 +2112,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:IW123"/>
+  <dimension ref="A1:IW118"/>
   <sheetFormatPr defaultColWidth="8.984375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="3.48"/>
@@ -2140,6 +2128,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="3.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="16.27"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="13" style="2" width="8.98"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="258" style="1" width="8.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,368 +5037,341 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>73</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="1" t="s">
         <v>72</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8" t="s">
+      <c r="E35" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="34"/>
+      <c r="B37" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="34"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="34"/>
+      <c r="W37" s="34"/>
+      <c r="X37" s="34"/>
+      <c r="Y37" s="34"/>
+      <c r="Z37" s="34"/>
+      <c r="AA37" s="34"/>
+      <c r="AB37" s="34"/>
+      <c r="AC37" s="34"/>
+      <c r="AD37" s="34"/>
+      <c r="AE37" s="34"/>
+      <c r="AF37" s="34"/>
+      <c r="AG37" s="34"/>
+      <c r="AH37" s="34"/>
+      <c r="AI37" s="34"/>
+      <c r="AJ37" s="34"/>
+      <c r="AK37" s="34"/>
+      <c r="AL37" s="34"/>
+      <c r="AM37" s="34"/>
+      <c r="AN37" s="34"/>
+      <c r="AO37" s="34"/>
+      <c r="AP37" s="34"/>
+      <c r="AQ37" s="34"/>
+      <c r="AR37" s="34"/>
+      <c r="AS37" s="34"/>
+      <c r="AT37" s="34"/>
+      <c r="AU37" s="34"/>
+      <c r="AV37" s="34"/>
+      <c r="AW37" s="34"/>
+      <c r="AX37" s="34"/>
+      <c r="AY37" s="34"/>
+      <c r="AZ37" s="34"/>
+      <c r="BA37" s="34"/>
+      <c r="BB37" s="34"/>
+      <c r="BC37" s="34"/>
+      <c r="BD37" s="34"/>
+      <c r="BE37" s="34"/>
+      <c r="BF37" s="34"/>
+      <c r="BG37" s="34"/>
+      <c r="BH37" s="34"/>
+      <c r="BI37" s="34"/>
+      <c r="BJ37" s="34"/>
+      <c r="BK37" s="34"/>
+      <c r="BL37" s="34"/>
+      <c r="BM37" s="34"/>
+      <c r="BN37" s="34"/>
+      <c r="BO37" s="34"/>
+      <c r="BP37" s="34"/>
+      <c r="BQ37" s="34"/>
+      <c r="BR37" s="34"/>
+      <c r="BS37" s="34"/>
+      <c r="BT37" s="34"/>
+      <c r="BU37" s="34"/>
+      <c r="BV37" s="34"/>
+      <c r="BW37" s="34"/>
+      <c r="BX37" s="34"/>
+      <c r="BY37" s="34"/>
+      <c r="BZ37" s="34"/>
+      <c r="CA37" s="34"/>
+      <c r="CB37" s="34"/>
+      <c r="CC37" s="34"/>
+      <c r="CD37" s="34"/>
+      <c r="CE37" s="34"/>
+      <c r="CF37" s="34"/>
+      <c r="CG37" s="34"/>
+      <c r="CH37" s="34"/>
+      <c r="CI37" s="34"/>
+      <c r="CJ37" s="34"/>
+      <c r="CK37" s="34"/>
+      <c r="CL37" s="34"/>
+      <c r="CM37" s="34"/>
+      <c r="CN37" s="34"/>
+      <c r="CO37" s="34"/>
+      <c r="CP37" s="34"/>
+      <c r="CQ37" s="34"/>
+      <c r="CR37" s="34"/>
+      <c r="CS37" s="34"/>
+      <c r="CT37" s="34"/>
+      <c r="CU37" s="34"/>
+      <c r="CV37" s="34"/>
+      <c r="CW37" s="34"/>
+      <c r="CX37" s="34"/>
+      <c r="CY37" s="34"/>
+      <c r="CZ37" s="34"/>
+      <c r="DA37" s="34"/>
+      <c r="DB37" s="34"/>
+      <c r="DC37" s="34"/>
+      <c r="DD37" s="34"/>
+      <c r="DE37" s="34"/>
+      <c r="DF37" s="34"/>
+      <c r="DG37" s="34"/>
+      <c r="DH37" s="34"/>
+      <c r="DI37" s="34"/>
+      <c r="DJ37" s="34"/>
+      <c r="DK37" s="34"/>
+      <c r="DL37" s="34"/>
+      <c r="DM37" s="34"/>
+      <c r="DN37" s="34"/>
+      <c r="DO37" s="34"/>
+      <c r="DP37" s="34"/>
+      <c r="DQ37" s="34"/>
+      <c r="DR37" s="34"/>
+      <c r="DS37" s="34"/>
+      <c r="DT37" s="34"/>
+      <c r="DU37" s="34"/>
+      <c r="DV37" s="34"/>
+      <c r="DW37" s="34"/>
+      <c r="DX37" s="34"/>
+      <c r="DY37" s="34"/>
+      <c r="DZ37" s="34"/>
+      <c r="EA37" s="34"/>
+      <c r="EB37" s="34"/>
+      <c r="EC37" s="34"/>
+      <c r="ED37" s="34"/>
+      <c r="EE37" s="34"/>
+      <c r="EF37" s="34"/>
+      <c r="EG37" s="34"/>
+      <c r="EH37" s="34"/>
+      <c r="EI37" s="34"/>
+      <c r="EJ37" s="34"/>
+      <c r="EK37" s="34"/>
+      <c r="EL37" s="34"/>
+      <c r="EM37" s="34"/>
+      <c r="EN37" s="34"/>
+      <c r="EO37" s="34"/>
+      <c r="EP37" s="34"/>
+      <c r="EQ37" s="34"/>
+      <c r="ER37" s="34"/>
+      <c r="ES37" s="34"/>
+      <c r="ET37" s="34"/>
+      <c r="EU37" s="34"/>
+      <c r="EV37" s="34"/>
+      <c r="EW37" s="34"/>
+      <c r="EX37" s="34"/>
+      <c r="EY37" s="34"/>
+      <c r="EZ37" s="34"/>
+      <c r="FA37" s="34"/>
+      <c r="FB37" s="34"/>
+      <c r="FC37" s="34"/>
+      <c r="FD37" s="34"/>
+      <c r="FE37" s="34"/>
+      <c r="FF37" s="34"/>
+      <c r="FG37" s="34"/>
+      <c r="FH37" s="34"/>
+      <c r="FI37" s="34"/>
+      <c r="FJ37" s="34"/>
+      <c r="FK37" s="34"/>
+      <c r="FL37" s="34"/>
+      <c r="FM37" s="34"/>
+      <c r="FN37" s="34"/>
+      <c r="FO37" s="34"/>
+      <c r="FP37" s="34"/>
+      <c r="FQ37" s="34"/>
+      <c r="FR37" s="34"/>
+      <c r="FS37" s="34"/>
+      <c r="FT37" s="34"/>
+      <c r="FU37" s="34"/>
+      <c r="FV37" s="34"/>
+      <c r="FW37" s="34"/>
+      <c r="FX37" s="34"/>
+      <c r="FY37" s="34"/>
+      <c r="FZ37" s="34"/>
+      <c r="GA37" s="34"/>
+      <c r="GB37" s="34"/>
+      <c r="GC37" s="34"/>
+      <c r="GD37" s="34"/>
+      <c r="GE37" s="34"/>
+      <c r="GF37" s="34"/>
+      <c r="GG37" s="34"/>
+      <c r="GH37" s="34"/>
+      <c r="GI37" s="34"/>
+      <c r="GJ37" s="34"/>
+      <c r="GK37" s="34"/>
+      <c r="GL37" s="34"/>
+      <c r="GM37" s="34"/>
+      <c r="GN37" s="34"/>
+      <c r="GO37" s="34"/>
+      <c r="GP37" s="34"/>
+      <c r="GQ37" s="34"/>
+      <c r="GR37" s="34"/>
+      <c r="GS37" s="34"/>
+      <c r="GT37" s="34"/>
+      <c r="GU37" s="34"/>
+      <c r="GV37" s="34"/>
+      <c r="GW37" s="34"/>
+      <c r="GX37" s="34"/>
+      <c r="GY37" s="34"/>
+      <c r="GZ37" s="34"/>
+      <c r="HA37" s="34"/>
+      <c r="HB37" s="34"/>
+      <c r="HC37" s="34"/>
+      <c r="HD37" s="34"/>
+      <c r="HE37" s="34"/>
+      <c r="HF37" s="34"/>
+      <c r="HG37" s="34"/>
+      <c r="HH37" s="34"/>
+      <c r="HI37" s="34"/>
+      <c r="HJ37" s="34"/>
+      <c r="HK37" s="34"/>
+      <c r="HL37" s="34"/>
+      <c r="HM37" s="34"/>
+      <c r="HN37" s="34"/>
+      <c r="HO37" s="34"/>
+      <c r="HP37" s="34"/>
+      <c r="HQ37" s="34"/>
+      <c r="HR37" s="34"/>
+      <c r="HS37" s="34"/>
+      <c r="HT37" s="34"/>
+      <c r="HU37" s="34"/>
+      <c r="HV37" s="34"/>
+      <c r="HW37" s="34"/>
+      <c r="HX37" s="34"/>
+      <c r="HY37" s="34"/>
+      <c r="HZ37" s="34"/>
+      <c r="IA37" s="34"/>
+      <c r="IB37" s="34"/>
+      <c r="IC37" s="34"/>
+      <c r="ID37" s="34"/>
+      <c r="IE37" s="34"/>
+      <c r="IF37" s="34"/>
+      <c r="IG37" s="34"/>
+      <c r="IH37" s="34"/>
+      <c r="II37" s="34"/>
+      <c r="IJ37" s="34"/>
+      <c r="IK37" s="34"/>
+      <c r="IL37" s="34"/>
+      <c r="IM37" s="34"/>
+      <c r="IN37" s="34"/>
+      <c r="IO37" s="34"/>
+      <c r="IP37" s="34"/>
+      <c r="IQ37" s="34"/>
+      <c r="IR37" s="34"/>
+      <c r="IS37" s="34"/>
+      <c r="IT37" s="34"/>
+      <c r="IU37" s="34"/>
+      <c r="IV37" s="34"/>
+      <c r="IW37" s="34"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E36" s="2" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="1"/>
-      <c r="C37" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="8" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1"/>
-      <c r="C40" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34"/>
-      <c r="B42" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="40"/>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="34"/>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="W42" s="34"/>
-      <c r="X42" s="34"/>
-      <c r="Y42" s="34"/>
-      <c r="Z42" s="34"/>
-      <c r="AA42" s="34"/>
-      <c r="AB42" s="34"/>
-      <c r="AC42" s="34"/>
-      <c r="AD42" s="34"/>
-      <c r="AE42" s="34"/>
-      <c r="AF42" s="34"/>
-      <c r="AG42" s="34"/>
-      <c r="AH42" s="34"/>
-      <c r="AI42" s="34"/>
-      <c r="AJ42" s="34"/>
-      <c r="AK42" s="34"/>
-      <c r="AL42" s="34"/>
-      <c r="AM42" s="34"/>
-      <c r="AN42" s="34"/>
-      <c r="AO42" s="34"/>
-      <c r="AP42" s="34"/>
-      <c r="AQ42" s="34"/>
-      <c r="AR42" s="34"/>
-      <c r="AS42" s="34"/>
-      <c r="AT42" s="34"/>
-      <c r="AU42" s="34"/>
-      <c r="AV42" s="34"/>
-      <c r="AW42" s="34"/>
-      <c r="AX42" s="34"/>
-      <c r="AY42" s="34"/>
-      <c r="AZ42" s="34"/>
-      <c r="BA42" s="34"/>
-      <c r="BB42" s="34"/>
-      <c r="BC42" s="34"/>
-      <c r="BD42" s="34"/>
-      <c r="BE42" s="34"/>
-      <c r="BF42" s="34"/>
-      <c r="BG42" s="34"/>
-      <c r="BH42" s="34"/>
-      <c r="BI42" s="34"/>
-      <c r="BJ42" s="34"/>
-      <c r="BK42" s="34"/>
-      <c r="BL42" s="34"/>
-      <c r="BM42" s="34"/>
-      <c r="BN42" s="34"/>
-      <c r="BO42" s="34"/>
-      <c r="BP42" s="34"/>
-      <c r="BQ42" s="34"/>
-      <c r="BR42" s="34"/>
-      <c r="BS42" s="34"/>
-      <c r="BT42" s="34"/>
-      <c r="BU42" s="34"/>
-      <c r="BV42" s="34"/>
-      <c r="BW42" s="34"/>
-      <c r="BX42" s="34"/>
-      <c r="BY42" s="34"/>
-      <c r="BZ42" s="34"/>
-      <c r="CA42" s="34"/>
-      <c r="CB42" s="34"/>
-      <c r="CC42" s="34"/>
-      <c r="CD42" s="34"/>
-      <c r="CE42" s="34"/>
-      <c r="CF42" s="34"/>
-      <c r="CG42" s="34"/>
-      <c r="CH42" s="34"/>
-      <c r="CI42" s="34"/>
-      <c r="CJ42" s="34"/>
-      <c r="CK42" s="34"/>
-      <c r="CL42" s="34"/>
-      <c r="CM42" s="34"/>
-      <c r="CN42" s="34"/>
-      <c r="CO42" s="34"/>
-      <c r="CP42" s="34"/>
-      <c r="CQ42" s="34"/>
-      <c r="CR42" s="34"/>
-      <c r="CS42" s="34"/>
-      <c r="CT42" s="34"/>
-      <c r="CU42" s="34"/>
-      <c r="CV42" s="34"/>
-      <c r="CW42" s="34"/>
-      <c r="CX42" s="34"/>
-      <c r="CY42" s="34"/>
-      <c r="CZ42" s="34"/>
-      <c r="DA42" s="34"/>
-      <c r="DB42" s="34"/>
-      <c r="DC42" s="34"/>
-      <c r="DD42" s="34"/>
-      <c r="DE42" s="34"/>
-      <c r="DF42" s="34"/>
-      <c r="DG42" s="34"/>
-      <c r="DH42" s="34"/>
-      <c r="DI42" s="34"/>
-      <c r="DJ42" s="34"/>
-      <c r="DK42" s="34"/>
-      <c r="DL42" s="34"/>
-      <c r="DM42" s="34"/>
-      <c r="DN42" s="34"/>
-      <c r="DO42" s="34"/>
-      <c r="DP42" s="34"/>
-      <c r="DQ42" s="34"/>
-      <c r="DR42" s="34"/>
-      <c r="DS42" s="34"/>
-      <c r="DT42" s="34"/>
-      <c r="DU42" s="34"/>
-      <c r="DV42" s="34"/>
-      <c r="DW42" s="34"/>
-      <c r="DX42" s="34"/>
-      <c r="DY42" s="34"/>
-      <c r="DZ42" s="34"/>
-      <c r="EA42" s="34"/>
-      <c r="EB42" s="34"/>
-      <c r="EC42" s="34"/>
-      <c r="ED42" s="34"/>
-      <c r="EE42" s="34"/>
-      <c r="EF42" s="34"/>
-      <c r="EG42" s="34"/>
-      <c r="EH42" s="34"/>
-      <c r="EI42" s="34"/>
-      <c r="EJ42" s="34"/>
-      <c r="EK42" s="34"/>
-      <c r="EL42" s="34"/>
-      <c r="EM42" s="34"/>
-      <c r="EN42" s="34"/>
-      <c r="EO42" s="34"/>
-      <c r="EP42" s="34"/>
-      <c r="EQ42" s="34"/>
-      <c r="ER42" s="34"/>
-      <c r="ES42" s="34"/>
-      <c r="ET42" s="34"/>
-      <c r="EU42" s="34"/>
-      <c r="EV42" s="34"/>
-      <c r="EW42" s="34"/>
-      <c r="EX42" s="34"/>
-      <c r="EY42" s="34"/>
-      <c r="EZ42" s="34"/>
-      <c r="FA42" s="34"/>
-      <c r="FB42" s="34"/>
-      <c r="FC42" s="34"/>
-      <c r="FD42" s="34"/>
-      <c r="FE42" s="34"/>
-      <c r="FF42" s="34"/>
-      <c r="FG42" s="34"/>
-      <c r="FH42" s="34"/>
-      <c r="FI42" s="34"/>
-      <c r="FJ42" s="34"/>
-      <c r="FK42" s="34"/>
-      <c r="FL42" s="34"/>
-      <c r="FM42" s="34"/>
-      <c r="FN42" s="34"/>
-      <c r="FO42" s="34"/>
-      <c r="FP42" s="34"/>
-      <c r="FQ42" s="34"/>
-      <c r="FR42" s="34"/>
-      <c r="FS42" s="34"/>
-      <c r="FT42" s="34"/>
-      <c r="FU42" s="34"/>
-      <c r="FV42" s="34"/>
-      <c r="FW42" s="34"/>
-      <c r="FX42" s="34"/>
-      <c r="FY42" s="34"/>
-      <c r="FZ42" s="34"/>
-      <c r="GA42" s="34"/>
-      <c r="GB42" s="34"/>
-      <c r="GC42" s="34"/>
-      <c r="GD42" s="34"/>
-      <c r="GE42" s="34"/>
-      <c r="GF42" s="34"/>
-      <c r="GG42" s="34"/>
-      <c r="GH42" s="34"/>
-      <c r="GI42" s="34"/>
-      <c r="GJ42" s="34"/>
-      <c r="GK42" s="34"/>
-      <c r="GL42" s="34"/>
-      <c r="GM42" s="34"/>
-      <c r="GN42" s="34"/>
-      <c r="GO42" s="34"/>
-      <c r="GP42" s="34"/>
-      <c r="GQ42" s="34"/>
-      <c r="GR42" s="34"/>
-      <c r="GS42" s="34"/>
-      <c r="GT42" s="34"/>
-      <c r="GU42" s="34"/>
-      <c r="GV42" s="34"/>
-      <c r="GW42" s="34"/>
-      <c r="GX42" s="34"/>
-      <c r="GY42" s="34"/>
-      <c r="GZ42" s="34"/>
-      <c r="HA42" s="34"/>
-      <c r="HB42" s="34"/>
-      <c r="HC42" s="34"/>
-      <c r="HD42" s="34"/>
-      <c r="HE42" s="34"/>
-      <c r="HF42" s="34"/>
-      <c r="HG42" s="34"/>
-      <c r="HH42" s="34"/>
-      <c r="HI42" s="34"/>
-      <c r="HJ42" s="34"/>
-      <c r="HK42" s="34"/>
-      <c r="HL42" s="34"/>
-      <c r="HM42" s="34"/>
-      <c r="HN42" s="34"/>
-      <c r="HO42" s="34"/>
-      <c r="HP42" s="34"/>
-      <c r="HQ42" s="34"/>
-      <c r="HR42" s="34"/>
-      <c r="HS42" s="34"/>
-      <c r="HT42" s="34"/>
-      <c r="HU42" s="34"/>
-      <c r="HV42" s="34"/>
-      <c r="HW42" s="34"/>
-      <c r="HX42" s="34"/>
-      <c r="HY42" s="34"/>
-      <c r="HZ42" s="34"/>
-      <c r="IA42" s="34"/>
-      <c r="IB42" s="34"/>
-      <c r="IC42" s="34"/>
-      <c r="ID42" s="34"/>
-      <c r="IE42" s="34"/>
-      <c r="IF42" s="34"/>
-      <c r="IG42" s="34"/>
-      <c r="IH42" s="34"/>
-      <c r="II42" s="34"/>
-      <c r="IJ42" s="34"/>
-      <c r="IK42" s="34"/>
-      <c r="IL42" s="34"/>
-      <c r="IM42" s="34"/>
-      <c r="IN42" s="34"/>
-      <c r="IO42" s="34"/>
-      <c r="IP42" s="34"/>
-      <c r="IQ42" s="34"/>
-      <c r="IR42" s="34"/>
-      <c r="IS42" s="34"/>
-      <c r="IT42" s="34"/>
-      <c r="IU42" s="34"/>
-      <c r="IV42" s="34"/>
-      <c r="IW42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5433,7 +5395,7 @@
         <v>28</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5441,7 +5403,7 @@
         <v>28</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5449,7 +5411,7 @@
         <v>28</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5457,1104 +5419,1064 @@
         <v>28</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="8" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="C54" s="8" t="s">
-        <v>90</v>
+        <v>46</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="B58" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="E58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="C59" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C63" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C64" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F61" s="41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="42" t="s">
+      <c r="G65" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K65" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="43" t="s">
+      <c r="L65" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="13"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C66" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L67" s="44" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C68" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>112</v>
+      <c r="L68" s="44" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C69" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>48</v>
+      <c r="K69" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L69" s="44" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C70" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>108</v>
+        <v>78</v>
+      </c>
+      <c r="E70" s="44" t="s">
+        <v>122</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>109</v>
+      <c r="L70" s="44" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C71" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>118</v>
+        <v>78</v>
+      </c>
+      <c r="E71" s="44" t="s">
+        <v>124</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>120</v>
+      <c r="L71" s="44" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C72" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="E72" s="44" t="s">
+        <v>126</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L72" s="44" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C73" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L73" s="44" t="s">
-        <v>124</v>
+      <c r="L73" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E74" s="44" t="s">
-        <v>125</v>
-      </c>
       <c r="F74" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L74" s="44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C75" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E75" s="44" t="s">
-        <v>127</v>
+        <v>78</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L75" s="44" t="s">
-        <v>128</v>
+      <c r="L75" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C76" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E76" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>119</v>
+        <v>78</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L76" s="44" t="s">
-        <v>130</v>
+      <c r="L76" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C77" s="2" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E77" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="F77" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D78" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L77" s="44" t="s">
+      <c r="E78" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F79" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>133</v>
+      <c r="C79" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C80" s="2" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C81" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D84" s="11"/>
+      <c r="E84" s="13"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C88" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C89" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C91" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D83" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C84" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C85" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C86" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C89" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D89" s="11"/>
-      <c r="E89" s="13"/>
-    </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C92" s="2" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="s">
         <v>109</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C93" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>48</v>
+        <v>103</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C94" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C95" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="C95" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D95" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95" s="11"/>
+      <c r="F95" s="13"/>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C96" s="2" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>48</v>
+      <c r="C97" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C98" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D99" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D100" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D101" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D102" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D103" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C99" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C100" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="13"/>
-    </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C102" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C103" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="2" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="s">
         <v>109</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C106" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D108" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E108" s="11"/>
+      <c r="F108" s="13"/>
+    </row>
+    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I105" s="2" t="s">
+      <c r="D110" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D111" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D112" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="J105" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K105" s="2" t="s">
+      <c r="G112" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C113" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D114" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D115" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D106" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D107" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F107" s="2" t="s">
+    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D108" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L108" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D109" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D110" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C111" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C113" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D113" s="43" t="s">
-        <v>148</v>
-      </c>
-      <c r="E113" s="11"/>
-      <c r="F113" s="13"/>
-    </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C114" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C115" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D116" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D117" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C118" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D119" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D120" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C121" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C122" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="2" t="s">
-        <v>98</v>
+      <c r="B118" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12ページ &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter/>
   </headerFooter>
 </worksheet>
 </file>
@@ -6573,7 +6495,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="46" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
@@ -6647,7 +6569,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="50" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
@@ -6686,7 +6608,7 @@
     <row r="5" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="49"/>
       <c r="C5" s="49" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
@@ -6724,7 +6646,7 @@
     <row r="6" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="49"/>
       <c r="C6" s="49" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
@@ -6762,7 +6684,7 @@
     <row r="7" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="49"/>
       <c r="C7" s="49" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
@@ -6800,7 +6722,7 @@
     <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="49"/>
       <c r="C8" s="49" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D8" s="49"/>
       <c r="E8" s="49"/>
@@ -6838,7 +6760,7 @@
     <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="49"/>
       <c r="C9" s="49" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="49"/>
@@ -6876,7 +6798,7 @@
     <row r="10" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="49"/>
       <c r="C10" s="49" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -6950,7 +6872,7 @@
     <row r="12" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="49"/>
       <c r="C12" s="49" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="49"/>
@@ -6989,7 +6911,7 @@
       <c r="B13" s="49"/>
       <c r="C13" s="49"/>
       <c r="D13" s="49" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="49"/>
@@ -7062,7 +6984,7 @@
     <row r="15" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="49"/>
       <c r="C15" s="49" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D15" s="49"/>
       <c r="E15" s="49"/>
@@ -7101,7 +7023,7 @@
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
       <c r="D16" s="53" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
@@ -7172,7 +7094,7 @@
     </row>
     <row r="18" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="50" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
@@ -7211,7 +7133,7 @@
     <row r="19" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="49"/>
       <c r="C19" s="49" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D19" s="49"/>
       <c r="E19" s="49"/>
@@ -7249,7 +7171,7 @@
     <row r="20" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="49"/>
       <c r="C20" s="49" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D20" s="49"/>
       <c r="E20" s="49"/>
@@ -7287,7 +7209,7 @@
     <row r="21" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="49"/>
       <c r="C21" s="49" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D21" s="49"/>
       <c r="E21" s="49"/>
@@ -7361,7 +7283,7 @@
     <row r="23" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49"/>
       <c r="B23" s="50" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -7401,7 +7323,7 @@
       <c r="A24" s="49"/>
       <c r="B24" s="49"/>
       <c r="C24" s="53" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D24" s="49"/>
       <c r="E24" s="49"/>
@@ -7440,7 +7362,7 @@
       <c r="A25" s="49"/>
       <c r="B25" s="49"/>
       <c r="C25" s="49" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D25" s="49"/>
       <c r="E25" s="49"/>
@@ -7478,7 +7400,7 @@
     <row r="26" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="49"/>
       <c r="C26" s="49" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D26" s="49"/>
       <c r="E26" s="49"/>
@@ -7515,7 +7437,7 @@
     </row>
     <row r="27" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="45" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
